--- a/POTAL_D14_Finance_Tracker.xlsx
+++ b/POTAL_D14_Finance_Tracker.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Monthly Costs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Division Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CW22B_NoCostChange" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly Costs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Division Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -501,6 +502,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="14" min="1" max="1"/>
+    <col width="70" customWidth="1" style="14" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:00 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>추가 비용</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>없음 — Supabase Auth 기본 기능 활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>인프라 비용</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>변동 없음: 고정 ~$114/월, 100만건 ~$140/월</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>이메일 인증은 Supabase Auth 내장 기능, 추가 과금 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -533,44 +612,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>2026-03-28 23:30 KST</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>v3 파이프라인 완성</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>AI 0회 → API 호출당 비용 $0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>수익 구조: API 비용 0, 순수 SaaS 마진</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>2026-03-28 23:30 KST</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>인프라 비용 변동</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>없음 — 코드 기반, 추가 인프라 불필요</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Vercel $20 + Supabase $25 유지</t>
         </is>
@@ -581,7 +660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1316,7 +1395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1694,7 +1773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
